--- a/MAJSushiConfig/ig/FRIntendedRecipientLMCDAFHIR.xlsx
+++ b/MAJSushiConfig/ig/FRIntendedRecipientLMCDAFHIR.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/ConceptMap/FRIntendedRecipientLMCDAFHIR</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/ConceptMap/FRIntendedRecipientLMCDAFHIR</t>
   </si>
   <si>
     <t>Version</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:25:17+00:00</t>
+    <t>2026-09-07T11:26:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMIntendedRecipient</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMIntendedRecipient|0.1.0</t>
   </si>
   <si>
     <t/>

--- a/MAJSushiConfig/ig/FRIntendedRecipientLMCDAFHIR.xlsx
+++ b/MAJSushiConfig/ig/FRIntendedRecipientLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="47">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T11:26:50+00:00</t>
+    <t>2026-09-07T11:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -136,6 +136,9 @@
   </si>
   <si>
     <t>FRLMIntendedRecipient.intendedRecipient[x].intendedRecipientOrganisation</t>
+  </si>
+  <si>
+    <t>FRLMOrganisation</t>
   </si>
   <si>
     <t>FRLMIntendedRecipient.intendedRecipient[x].intendedRecipientPatient</t>
@@ -478,7 +481,9 @@
       <c r="A5" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" t="s" s="2">
+        <v>40</v>
+      </c>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
@@ -489,7 +494,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
@@ -502,7 +507,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
@@ -515,7 +520,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
@@ -564,7 +569,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -579,7 +584,7 @@
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -592,7 +597,7 @@
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E4" s="2"/>
     </row>
@@ -600,51 +605,53 @@
       <c r="A5" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" t="s" s="2">
+        <v>40</v>
+      </c>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E8" s="2"/>
     </row>
